--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5003E7CE-AAB4-4EF5-AE4E-D7E443B437A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A01656-3522-4ED6-A1D6-68FE220AC788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="885" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guides" sheetId="1" r:id="rId1"/>
@@ -29,29 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>Раздел 1</t>
-  </si>
-  <si>
-    <t>1.jpg, 2.jpg</t>
-  </si>
-  <si>
-    <t>1.mp4, 2.mp4</t>
-  </si>
-  <si>
-    <t>Раздел 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">текст раздела  текст раздела  текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела </t>
-  </si>
-  <si>
-    <t xml:space="preserve">текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела текст раздела </t>
-  </si>
-  <si>
     <t>title</t>
   </si>
   <si>
@@ -64,24 +46,12 @@
     <t>date</t>
   </si>
   <si>
-    <t>Иванов И.И.</t>
-  </si>
-  <si>
     <t>img/html.jpg</t>
   </si>
   <si>
-    <t>HTML основы</t>
-  </si>
-  <si>
-    <t>CSS руководство</t>
-  </si>
-  <si>
     <t>img/css.jpg</t>
   </si>
   <si>
-    <t>Петров П.П.</t>
-  </si>
-  <si>
     <t>guide_id</t>
   </si>
   <si>
@@ -95,6 +65,46 @@
   </si>
   <si>
     <t>videos</t>
+  </si>
+  <si>
+    <t>Некоторые вопросы федерального закона "О связи"</t>
+  </si>
+  <si>
+    <t>Цели</t>
+  </si>
+  <si>
+    <t>ТИПК МВД</t>
+  </si>
+  <si>
+    <t>Некоторые цели закона:
+&lt;q&gt;создание условий для оказания услуг связи на всей территории Российской Федерации;&lt;/q&gt;
+содействие внедрению перспективных технологий;
+защита интересов пользователей услугами связи и осуществляющих деятельность в области связи хозяйствующих субъектов;
+обеспечение эффективной и добросовестной конкуренции на рынке услуг связи;
+создание условий для развития российской инфраструктуры связи, обеспечения её интеграции с международными сетями связи;
+обеспечение централизованного управления российскими радиочастотным ресурсом, в том числе орбитально-частотным, и ресурсом нумерации;
+создание условий для обеспечения потребностей в связи для нужд органов государственной власти, нужд обороны страны, безопасности государства и обеспечения правопорядка.</t>
+  </si>
+  <si>
+    <t>Сфера действия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закон регулирует отношения, связанные с созданием и эксплуатацией всех сетей связи и сооружений связи, использованием радиочастотного спектра, оказанием услуг электросвязи и почтовой связи на территории Российской Федерации и на находящихся под её юрисдикцией территориях. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уголовный кодекс Российской Федерации (УК РФ) </t>
+  </si>
+  <si>
+    <t>Принят</t>
+  </si>
+  <si>
+    <t>Основан</t>
+  </si>
+  <si>
+    <t>Основан на Конституции России, общепризнанных принципах и нормах международного права, а также на нормах, содержащихся в международно-правовых обязательствах России. </t>
+  </si>
+  <si>
+    <t>Государственной Думой 24 мая 1996 года, одобрен Советом Федерации 5 июня 1996 года, подписан президентом 13 июня 1996 года. Вступил в силу с 1 января 1997 года, сменив Уголовный кодекс РСФСР 1960 года.</t>
   </si>
 </sst>
 </file>
@@ -130,9 +140,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -428,16 +441,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -445,16 +458,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1">
-        <v>45306</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -462,16 +475,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" s="1">
-        <v>45342</v>
+        <v>46134</v>
       </c>
     </row>
   </sheetData>
@@ -482,12 +495,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A69A83A-8BDF-4317-B0E2-0EEE11B3C722}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="65.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" customWidth="1"/>
@@ -498,25 +511,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="255" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -524,22 +537,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -547,22 +551,42 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A01656-3522-4ED6-A1D6-68FE220AC788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C681654-F45C-4465-BBFF-DACD83A78FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="885" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,35 +76,35 @@
     <t>ТИПК МВД</t>
   </si>
   <si>
+    <t>Сфера действия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Закон регулирует отношения, связанные с созданием и эксплуатацией всех сетей связи и сооружений связи, использованием радиочастотного спектра, оказанием услуг электросвязи и почтовой связи на территории Российской Федерации и на находящихся под её юрисдикцией территориях. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уголовный кодекс Российской Федерации (УК РФ) </t>
+  </si>
+  <si>
+    <t>Принят</t>
+  </si>
+  <si>
+    <t>Основан</t>
+  </si>
+  <si>
+    <t>Основан на Конституции России, общепризнанных принципах и нормах международного права, а также на нормах, содержащихся в международно-правовых обязательствах России. </t>
+  </si>
+  <si>
+    <t>Государственной Думой 24 мая 1996 года, одобрен Советом Федерации 5 июня 1996 года, подписан президентом 13 июня 1996 года. Вступил в силу с 1 января 1997 года, сменив Уголовный кодекс РСФСР 1960 года.</t>
+  </si>
+  <si>
     <t>Некоторые цели закона:
 &lt;q&gt;создание условий для оказания услуг связи на всей территории Российской Федерации;&lt;/q&gt;
-содействие внедрению перспективных технологий;
-защита интересов пользователей услугами связи и осуществляющих деятельность в области связи хозяйствующих субъектов;
-обеспечение эффективной и добросовестной конкуренции на рынке услуг связи;
-создание условий для развития российской инфраструктуры связи, обеспечения её интеграции с международными сетями связи;
+&lt;c&gt;содействие внедрению перспективных технологий;
+защита интересов пользователей услугами связи и осуществляющих деятельность в области связи хозяйствующих субъектов;&lt;/c&gt;
+&lt;w&gt;обеспечение эффективной и добросовестной конкуренции на рынке услуг связи;&lt;/w&gt;
+&lt;e&gt;создание условий для развития российской инфраструктуры связи, обеспечения её интеграции с международными сетями связи;&lt;/e&gt;
 обеспечение централизованного управления российскими радиочастотным ресурсом, в том числе орбитально-частотным, и ресурсом нумерации;
 создание условий для обеспечения потребностей в связи для нужд органов государственной власти, нужд обороны страны, безопасности государства и обеспечения правопорядка.</t>
-  </si>
-  <si>
-    <t>Сфера действия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Закон регулирует отношения, связанные с созданием и эксплуатацией всех сетей связи и сооружений связи, использованием радиочастотного спектра, оказанием услуг электросвязи и почтовой связи на территории Российской Федерации и на находящихся под её юрисдикцией территориях. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уголовный кодекс Российской Федерации (УК РФ) </t>
-  </si>
-  <si>
-    <t>Принят</t>
-  </si>
-  <si>
-    <t>Основан</t>
-  </si>
-  <si>
-    <t>Основан на Конституции России, общепризнанных принципах и нормах международного права, а также на нормах, содержащихся в международно-правовых обязательствах России. </t>
-  </si>
-  <si>
-    <t>Государственной Думой 24 мая 1996 года, одобрен Советом Федерации 5 июня 1996 года, подписан президентом 13 июня 1996 года. Вступил в силу с 1 января 1997 года, сменив Уголовный кодекс РСФСР 1960 года.</t>
   </si>
 </sst>
 </file>
@@ -475,7 +475,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -529,7 +529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="255" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -540,7 +540,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -551,10 +551,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -565,10 +565,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -579,10 +579,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C681654-F45C-4465-BBFF-DACD83A78FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F218FC2-045E-4E10-86A4-D4DE24AEF58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="885" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,10 @@
 &lt;w&gt;обеспечение эффективной и добросовестной конкуренции на рынке услуг связи;&lt;/w&gt;
 &lt;e&gt;создание условий для развития российской инфраструктуры связи, обеспечения её интеграции с международными сетями связи;&lt;/e&gt;
 обеспечение централизованного управления российскими радиочастотным ресурсом, в том числе орбитально-частотным, и ресурсом нумерации;
-создание условий для обеспечения потребностей в связи для нужд органов государственной власти, нужд обороны страны, безопасности государства и обеспечения правопорядка.</t>
+создание условий для обеспечения потребностей в связи для нужд органов государственной власти, нужд обороны страны, безопасности государства и обеспечения правопорядка.Преимущества:
+&lt;ul&gt;&lt;li&gt;Быстро&lt;/li&gt;&lt;li&gt;Надёжно&lt;/li&gt;&lt;li&gt;Бесплатно&lt;/li&gt;&lt;/ul&gt;
+Инструкция:
+&lt;ol&gt;&lt;li&gt;Скачайте файл&lt;/li&gt;&lt;li&gt;Установите программу&lt;/li&gt;&lt;li&gt;Запустите&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
 </sst>
 </file>
@@ -529,7 +532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="270" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="345" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F218FC2-045E-4E10-86A4-D4DE24AEF58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26233543-D899-4EC3-AA7D-A0EAF6A8FBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="885" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guides" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,8 @@
 &lt;w&gt;обеспечение эффективной и добросовестной конкуренции на рынке услуг связи;&lt;/w&gt;
 &lt;e&gt;создание условий для развития российской инфраструктуры связи, обеспечения её интеграции с международными сетями связи;&lt;/e&gt;
 обеспечение централизованного управления российскими радиочастотным ресурсом, в том числе орбитально-частотным, и ресурсом нумерации;
-создание условий для обеспечения потребностей в связи для нужд органов государственной власти, нужд обороны страны, безопасности государства и обеспечения правопорядка.Преимущества:
+создание условий для обеспечения потребностей в связи для нужд органов государственной власти, нужд обороны страны, безопасности государства и обеспечения правопорядка.
+Преимущества:
 &lt;ul&gt;&lt;li&gt;Быстро&lt;/li&gt;&lt;li&gt;Надёжно&lt;/li&gt;&lt;li&gt;Бесплатно&lt;/li&gt;&lt;/ul&gt;
 Инструкция:
 &lt;ol&gt;&lt;li&gt;Скачайте файл&lt;/li&gt;&lt;li&gt;Установите программу&lt;/li&gt;&lt;li&gt;Запустите&lt;/li&gt;&lt;/ol&gt;</t>
@@ -532,7 +533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="345" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="360" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26233543-D899-4EC3-AA7D-A0EAF6A8FBF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DF22A0-99D2-4FF8-83EF-A0613FA9319F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="360" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="390" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DF22A0-99D2-4FF8-83EF-A0613FA9319F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB68E2C5-6FDD-405B-A022-DFAC2997EB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -109,6 +109,18 @@
 &lt;ul&gt;&lt;li&gt;Быстро&lt;/li&gt;&lt;li&gt;Надёжно&lt;/li&gt;&lt;li&gt;Бесплатно&lt;/li&gt;&lt;/ul&gt;
 Инструкция:
 &lt;ol&gt;&lt;li&gt;Скачайте файл&lt;/li&gt;&lt;li&gt;Установите программу&lt;/li&gt;&lt;li&gt;Запустите&lt;/li&gt;&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t>/video.mp4, https://rutube.ru/video/97155fee680a23619c044d4e9996238d/?r=wd</t>
+  </si>
+  <si>
+    <t>/1.jpg, /2.jpg</t>
+  </si>
+  <si>
+    <t>/video.mp4</t>
+  </si>
+  <si>
+    <t>https://rutube.ru/video/97155fee680a23619c044d4e9996238d/?r=wd</t>
   </si>
 </sst>
 </file>
@@ -144,12 +156,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -546,6 +559,12 @@
       <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -560,6 +579,9 @@
       <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -574,6 +596,9 @@
       <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -587,6 +612,9 @@
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB68E2C5-6FDD-405B-A022-DFAC2997EB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0134968-7705-407B-B4A8-103F478AF85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,16 +111,16 @@
 &lt;ol&gt;&lt;li&gt;Скачайте файл&lt;/li&gt;&lt;li&gt;Установите программу&lt;/li&gt;&lt;li&gt;Запустите&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
-    <t>/video.mp4, https://rutube.ru/video/97155fee680a23619c044d4e9996238d/?r=wd</t>
-  </si>
-  <si>
     <t>/1.jpg, /2.jpg</t>
   </si>
   <si>
     <t>/video.mp4</t>
   </si>
   <si>
-    <t>https://rutube.ru/video/97155fee680a23619c044d4e9996238d/?r=wd</t>
+    <t>/video.mp4, https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
+  </si>
+  <si>
+    <t>https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
   </si>
 </sst>
 </file>
@@ -560,10 +560,10 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -580,7 +580,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -614,7 +614,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0134968-7705-407B-B4A8-103F478AF85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62533DE-203B-47F5-8FCD-260A4DF9C707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,12 +46,6 @@
     <t>date</t>
   </si>
   <si>
-    <t>img/html.jpg</t>
-  </si>
-  <si>
-    <t>img/css.jpg</t>
-  </si>
-  <si>
     <t>guide_id</t>
   </si>
   <si>
@@ -111,16 +105,22 @@
 &lt;ol&gt;&lt;li&gt;Скачайте файл&lt;/li&gt;&lt;li&gt;Установите программу&lt;/li&gt;&lt;li&gt;Запустите&lt;/li&gt;&lt;/ol&gt;</t>
   </si>
   <si>
-    <t>/1.jpg, /2.jpg</t>
-  </si>
-  <si>
-    <t>/video.mp4</t>
-  </si>
-  <si>
-    <t>/video.mp4, https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
-  </si>
-  <si>
     <t>https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
+  </si>
+  <si>
+    <t>/video/video.mp4, https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
+  </si>
+  <si>
+    <t>/video/video.mp4</t>
+  </si>
+  <si>
+    <t>/img/guides/ykrf.png</t>
+  </si>
+  <si>
+    <t>/img/guides/ozosvizi.png</t>
+  </si>
+  <si>
+    <t>/img/placeholders/1.jpg, /img/placeholders/2.jpg</t>
   </si>
 </sst>
 </file>
@@ -162,7 +162,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -448,7 +450,7 @@
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" customWidth="1"/>
   </cols>
@@ -475,13 +477,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
       </c>
       <c r="E2" s="1">
         <v>46132</v>
@@ -492,13 +494,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1">
         <v>46134</v>
@@ -518,103 +520,110 @@
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="65.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="7" max="7" width="91.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="390" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="390" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/guide.xlsx
+++ b/docs/guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62533DE-203B-47F5-8FCD-260A4DF9C707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453F0C87-FA10-4AB9-BAFD-294F9776913C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guides" sheetId="1" r:id="rId1"/>
@@ -108,19 +108,19 @@
     <t>https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
   </si>
   <si>
-    <t>/video/video.mp4, https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
-  </si>
-  <si>
-    <t>/video/video.mp4</t>
-  </si>
-  <si>
-    <t>/img/guides/ykrf.png</t>
-  </si>
-  <si>
-    <t>/img/guides/ozosvizi.png</t>
-  </si>
-  <si>
-    <t>/img/placeholders/1.jpg, /img/placeholders/2.jpg</t>
+    <t>img/placeholders/1.jpg, img/placeholders/2.jpg</t>
+  </si>
+  <si>
+    <t>video/video.mp4, https://rutube.ru/play/embed/97155fee680a23619c044d4e9996238d/</t>
+  </si>
+  <si>
+    <t>video/video.mp4</t>
+  </si>
+  <si>
+    <t>img/guides/ykrf.png</t>
+  </si>
+  <si>
+    <t>img/guides/ozosvizi.png</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -497,7 +497,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -562,11 +562,11 @@
         <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -584,7 +584,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G3" s="2"/>
     </row>
@@ -623,7 +623,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
